--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486786_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486786_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.3895</v>
+        <v>8.672000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8113</v>
+        <v>5.5904</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5782</v>
+        <v>3.0815</v>
       </c>
       <c r="G2" t="n">
         <v>5.8302</v>
@@ -610,13 +610,13 @@
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9108000000000001</v>
+        <v>1.1933</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5243</v>
+        <v>0.2548</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4351</v>
+        <v>0.9385</v>
       </c>
       <c r="V2" t="n">
         <v>1.8415</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5216</v>
+        <v>7.0608</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3618</v>
+        <v>3.7272</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1598</v>
+        <v>3.3336</v>
       </c>
       <c r="G3" t="n">
         <v>4.2293</v>
@@ -688,13 +688,13 @@
         <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8056</v>
+        <v>1.3449</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3031</v>
+        <v>0.6685</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.6763</v>
       </c>
       <c r="V3" t="n">
         <v>0.3282</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>L. BULASHVILI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5994</v>
+        <v>5.8146</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8309</v>
+        <v>1.7471</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7685</v>
+        <v>4.0674</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4712</v>
+        <v>3.5385</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9792</v>
+        <v>0.8414</v>
       </c>
       <c r="I4" t="n">
-        <v>1.492</v>
+        <v>2.697</v>
       </c>
       <c r="J4" t="n">
-        <v>3.569</v>
+        <v>2.7677</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3248</v>
+        <v>1.0494</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2442</v>
+        <v>1.7182</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9022</v>
+        <v>0.7708</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3456</v>
+        <v>-0.208</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2478</v>
+        <v>0.9788</v>
       </c>
       <c r="P4" t="n">
         <v>-0.7723</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3169</v>
+        <v>-3.2823</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5446</v>
+        <v>2.51</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5723</v>
+        <v>1.2069</v>
       </c>
       <c r="T4" t="n">
-        <v>0.965</v>
+        <v>0.4203</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6073</v>
+        <v>0.7866</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3282</v>
+        <v>1.8415</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6138</v>
+        <v>1.8415</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. BULASHVILI</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.0711</v>
+        <v>4.9582</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3265</v>
+        <v>2.3138</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7446</v>
+        <v>2.6444</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5385</v>
+        <v>4.4712</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8414</v>
+        <v>2.9792</v>
       </c>
       <c r="I5" t="n">
-        <v>2.697</v>
+        <v>1.492</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7677</v>
+        <v>3.569</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0494</v>
+        <v>3.3248</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7182</v>
+        <v>0.2442</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7708</v>
+        <v>0.9022</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.208</v>
+        <v>-0.3456</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9788</v>
+        <v>1.2478</v>
       </c>
       <c r="P5" t="n">
         <v>-0.7723</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2823</v>
+        <v>-2.3169</v>
       </c>
       <c r="R5" t="n">
-        <v>2.51</v>
+        <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4635</v>
+        <v>0.9311</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0004</v>
+        <v>0.4479</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4638</v>
+        <v>0.4831</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8415</v>
+        <v>0.3282</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8415</v>
+        <v>0.6138</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3389</v>
+        <v>3.2907</v>
       </c>
       <c r="E6" t="n">
-        <v>0.654</v>
+        <v>0.6058</v>
       </c>
       <c r="F6" t="n">
         <v>2.6849</v>
@@ -922,10 +922,10 @@
         <v>1.1585</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2758</v>
+        <v>0.2276</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2756</v>
+        <v>0.2273</v>
       </c>
       <c r="U6" t="n">
         <v>0.0002</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6812</v>
+        <v>1.3362</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8831</v>
+        <v>-1.1039</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5643</v>
+        <v>2.4402</v>
       </c>
       <c r="G7" t="n">
         <v>2.7603</v>
@@ -1000,13 +1000,13 @@
         <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.345</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1657</v>
+        <v>0.6135</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8557</v>
+        <v>0.7315</v>
       </c>
       <c r="V7" t="n">
         <v>0.8995</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.514</v>
+        <v>0.4616</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6067</v>
+        <v>-0.7584</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1207</v>
+        <v>1.22</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7035</v>
@@ -1078,13 +1078,13 @@
         <v>1.7377</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0936</v>
+        <v>0.0413</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0273</v>
+        <v>-0.1244</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0663</v>
+        <v>0.1657</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6138</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>D. GABALDÓN CASTELLANOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9788</v>
+        <v>-0.9792</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3241</v>
+        <v>-0.7447</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3453</v>
+        <v>-0.2346</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5522</v>
+        <v>-0.9654</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7443</v>
+        <v>-0.4138</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1921</v>
+        <v>-0.5516</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3583</v>
+        <v>-0.6895</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.399</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0407</v>
+        <v>-0.6895</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1939</v>
+        <v>-0.2759</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3453</v>
+        <v>-0.4138</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1514</v>
+        <v>0.1379</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7377</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2798</v>
+        <v>-0.0138</v>
       </c>
       <c r="T9" t="n">
-        <v>0.965</v>
+        <v>-0.0552</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3147</v>
+        <v>0.0414</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. GABALDÓN CASTELLANOS</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0041</v>
+        <v>-1.2862</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7447</v>
+        <v>-1.7308</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2594</v>
+        <v>0.4446</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9654</v>
+        <v>-0.5522</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4138</v>
+        <v>-0.7443</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5516</v>
+        <v>0.1921</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6895</v>
+        <v>-0.3583</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.399</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6895</v>
+        <v>0.0407</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2759</v>
+        <v>-0.1939</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4138</v>
+        <v>-0.3453</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1379</v>
+        <v>0.1514</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.7377</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0386</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0552</v>
+        <v>0.5583</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0166</v>
+        <v>0.414</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.195</v>
+        <v>-1.8389</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0177</v>
+        <v>-2.6865</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8227</v>
+        <v>0.8476</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3726</v>
@@ -1312,13 +1312,13 @@
         <v>1.5446</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1197</v>
+        <v>0.4758</v>
       </c>
       <c r="T11" t="n">
-        <v>0.965</v>
+        <v>0.2963</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1547</v>
+        <v>0.1795</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5559</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>26.9378</v>
+        <v>27.4898</v>
       </c>
       <c r="E12" t="n">
-        <v>6.408200000000001</v>
+        <v>6.959999999999997</v>
       </c>
       <c r="F12" t="n">
         <v>20.5296</v>
@@ -1378,7 +1378,7 @@
         <v>-3.4544</v>
       </c>
       <c r="O12" t="n">
-        <v>6.996300000000001</v>
+        <v>6.9963</v>
       </c>
       <c r="P12" t="n">
         <v>-1.9308</v>
@@ -1390,16 +1390,16 @@
         <v>16.4116</v>
       </c>
       <c r="S12" t="n">
-        <v>7.1725</v>
+        <v>7.724399999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7554</v>
+        <v>3.3073</v>
       </c>
       <c r="U12" t="n">
-        <v>4.4169</v>
+        <v>4.4168</v>
       </c>
       <c r="V12" t="n">
-        <v>2.868799999999999</v>
+        <v>2.868799999999998</v>
       </c>
       <c r="W12" t="n">
         <v>6.709499999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9257</v>
+        <v>0.5906</v>
       </c>
       <c r="E13" t="n">
-        <v>1.35</v>
+        <v>1.0397</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4242</v>
+        <v>-0.449</v>
       </c>
       <c r="G13" t="n">
         <v>1.6404</v>
@@ -1468,13 +1468,13 @@
         <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>0.011</v>
+        <v>-0.3241</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0273</v>
+        <v>-0.283</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0163</v>
+        <v>-0.0411</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8842</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. GONZALEZ NOGALES</t>
+          <t>D. GARCIA NAVARO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2789</v>
+        <v>-0.3501</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6197</v>
+        <v>0.6263</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8986</v>
+        <v>-0.9764</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.6873</v>
+        <v>-1.3607</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1998</v>
+        <v>-2.0479</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.4875</v>
+        <v>0.6872</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1825</v>
+        <v>0.6748</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8697</v>
+        <v>-0.668</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6872</v>
+        <v>1.3428</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.8698</v>
+        <v>-2.0355</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0695</v>
+        <v>-1.3799</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8003</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9654</v>
+        <v>2.1239</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9654</v>
+        <v>2.1239</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8605</v>
+        <v>-0.8277</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8547</v>
+        <v>-0.6624</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0058</v>
+        <v>-0.1652</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5133</v>
+        <v>-0.2856</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5133</v>
+        <v>0.6138</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. LUENGO NEVADO</t>
+          <t>J. GONZALEZ NOGALES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.0967</v>
+        <v>-0.7534</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.06900000000000001</v>
+        <v>1.206</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0277</v>
+        <v>-1.9594</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8484</v>
+        <v>-1.6873</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4415</v>
+        <v>-0.1998</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4069</v>
+        <v>-1.4875</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0414</v>
+        <v>1.1825</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0414</v>
+        <v>1.8697</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.6872</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8898</v>
+        <v>-2.8698</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4829</v>
+        <v>-2.0695</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4069</v>
+        <v>-0.8003</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2483</v>
+        <v>0.386</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1104</v>
+        <v>0.441</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1379</v>
+        <v>-0.0549</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. GARCIA NAVARO</t>
+          <t>C. LUENGO NEVADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.15</v>
+        <v>-0.8898</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2126</v>
+        <v>0.1379</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3626</v>
+        <v>-1.0277</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3607</v>
+        <v>-0.8484</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.0479</v>
+        <v>-0.4415</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6872</v>
+        <v>-0.4069</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6748</v>
+        <v>0.0414</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.668</v>
+        <v>0.0414</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3428</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0355</v>
+        <v>-0.8898</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3799</v>
+        <v>-0.4829</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.4069</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1239</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1239</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6276</v>
+        <v>-0.0414</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0761</v>
+        <v>0.0965</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5515</v>
+        <v>-0.1379</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. LOPEZ MARQUEZ</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5385</v>
+        <v>-1.3178</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7178</v>
+        <v>-0.3449</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8208</v>
+        <v>-0.9729</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4282</v>
+        <v>-0.4624</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0619</v>
+        <v>-0.3312</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3662</v>
+        <v>-0.1311</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6074000000000001</v>
+        <v>0.0828</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6481</v>
+        <v>0.0828</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0407</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8208</v>
+        <v>-0.5451</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4138</v>
+        <v>-0.414</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4069</v>
+        <v>-0.1311</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.7723</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1104</v>
+        <v>-0.207</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1104</v>
+        <v>-0.2346</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.0277</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>K. LOPEZ MARQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6239</v>
+        <v>-1.4351</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5518</v>
+        <v>-0.6143</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0722</v>
+        <v>-0.8208</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4624</v>
+        <v>-1.4282</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3312</v>
+        <v>-1.0619</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1311</v>
+        <v>-0.3662</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0828</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0828</v>
+        <v>-0.6481</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0407</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5451</v>
+        <v>-0.8208</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.414</v>
+        <v>-0.4138</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1311</v>
+        <v>-0.4069</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5131</v>
+        <v>-0.0069</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4415</v>
+        <v>-0.0069</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0717</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8536</v>
+        <v>-1.7157</v>
       </c>
       <c r="E19" t="n">
         <v>-2.8523</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9987</v>
+        <v>1.1366</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3365</v>
@@ -1936,13 +1936,13 @@
         <v>2.51</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9379</v>
+        <v>-0.8</v>
       </c>
       <c r="T19" t="n">
         <v>-0.497</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4409</v>
+        <v>-0.303</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. PEREZ FERNANDEZ</t>
+          <t>L. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2458</v>
+        <v>-3.1262</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1328</v>
+        <v>-1.9733</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.113</v>
+        <v>-1.1529</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1839</v>
+        <v>-1.2847</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5034</v>
+        <v>-0.5522</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6804</v>
+        <v>-0.7325</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1411</v>
+        <v>0.7509</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7043</v>
+        <v>0.8277</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8454</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0428</v>
+        <v>-2.0355</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2077</v>
+        <v>-1.3799</v>
       </c>
       <c r="O20" t="n">
-        <v>0.165</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7031</v>
+        <v>2.3169</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8496</v>
+        <v>-1</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6901</v>
+        <v>-0.7934</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1595</v>
+        <v>-0.2066</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9847</v>
+        <v>-1.2277</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6138</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. ALONSO MENOR</t>
+          <t>M. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5495</v>
+        <v>-3.271</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2835</v>
+        <v>-5.0882</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2659</v>
+        <v>1.8172</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2847</v>
+        <v>-4.5097</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5522</v>
+        <v>-2.1722</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7325</v>
+        <v>-2.3375</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7509</v>
+        <v>-4.7229</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8277</v>
+        <v>-1.965</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-2.7579</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0355</v>
+        <v>0.2132</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3799</v>
+        <v>-0.2072</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.4205</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3862</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9308</v>
+        <v>-2.1239</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3169</v>
+        <v>1.7377</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4233</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1036</v>
+        <v>-0.6968</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3196</v>
+        <v>0.1519</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2277</v>
+        <v>2.1698</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.4554</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ALONSO MENOR</t>
+          <t>P. PEREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5757</v>
+        <v>-3.5134</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.1916</v>
+        <v>-3.3396</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6159</v>
+        <v>-0.1738</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.5097</v>
+        <v>-2.1839</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1722</v>
+        <v>-1.5034</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3375</v>
+        <v>-0.6804</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.7229</v>
+        <v>-0.1411</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.965</v>
+        <v>0.7043</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.7579</v>
+        <v>-0.8454</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2132</v>
+        <v>-2.0428</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2072</v>
+        <v>-2.2077</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4205</v>
+        <v>0.165</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1239</v>
+        <v>-1.9308</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7377</v>
+        <v>2.7031</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8496</v>
+        <v>-1.1172</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8002</v>
+        <v>-0.8969</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0494</v>
+        <v>-0.2203</v>
       </c>
       <c r="V22" t="n">
-        <v>2.1698</v>
+        <v>-0.9847</v>
       </c>
       <c r="W22" t="n">
-        <v>2.4554</v>
+        <v>-0.3709</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2856</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5516</v>
+        <v>-4.6247</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9133</v>
+        <v>-4.2236</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6383</v>
+        <v>-0.4011</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6486</v>
@@ -2248,13 +2248,13 @@
         <v>2.3169</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8718</v>
+        <v>-0.9448</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3038</v>
+        <v>-0.6141</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.3307</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3282</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3993</v>
+        <v>-5.1524</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9998</v>
+        <v>-5.1032</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3995</v>
+        <v>-0.0492</v>
       </c>
       <c r="G24" t="n">
         <v>-5.7175</v>
@@ -2326,13 +2326,13 @@
         <v>1.7377</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6125</v>
+        <v>-0.3657</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1659</v>
+        <v>-0.2693</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4466</v>
+        <v>-0.0963</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6138</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-26.9378</v>
+        <v>-25.559</v>
       </c>
       <c r="E25" t="n">
-        <v>-20.5296</v>
+        <v>-20.5295</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.4082</v>
+        <v>-5.0294</v>
       </c>
       <c r="G25" t="n">
         <v>-18.8275</v>
@@ -2380,7 +2380,7 @@
         <v>-3.5419</v>
       </c>
       <c r="K25" t="n">
-        <v>3.454400000000001</v>
+        <v>3.4544</v>
       </c>
       <c r="L25" t="n">
         <v>-6.9963</v>
@@ -2404,13 +2404,13 @@
         <v>18.3424</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.1726</v>
+        <v>-5.7937</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.417</v>
+        <v>-4.4169</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.7556</v>
+        <v>-1.3764</v>
       </c>
       <c r="V25" t="n">
         <v>-2.8688</v>
